--- a/public/jamin_record.xlsx
+++ b/public/jamin_record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Desktop\jamin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6B9F1F-0E7A-44AD-966E-E5F9DB790AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB381DE-5E4C-489B-9528-6984B0778664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="113">
   <si>
     <t>0.3.7</t>
   </si>
@@ -306,6 +306,78 @@
   </si>
   <si>
     <t xml:space="preserve">Remove from list not </t>
+  </si>
+  <si>
+    <t>localName</t>
+  </si>
+  <si>
+    <t>धोबी वाला</t>
+  </si>
+  <si>
+    <t>सेमर वाला उत्तर</t>
+  </si>
+  <si>
+    <t>दादी जीएन</t>
+  </si>
+  <si>
+    <t>9568/12404</t>
+  </si>
+  <si>
+    <t>भसुव्वा आम</t>
+  </si>
+  <si>
+    <t>क्रिकेट बगीचा</t>
+  </si>
+  <si>
+    <t>नगेशेर वाला</t>
+  </si>
+  <si>
+    <t>चाभ बस</t>
+  </si>
+  <si>
+    <t>घर बगीचा</t>
+  </si>
+  <si>
+    <t>घर बॉस</t>
+  </si>
+  <si>
+    <t>घर लीची</t>
+  </si>
+  <si>
+    <t>खरबन्ना</t>
+  </si>
+  <si>
+    <t>स्कूल क पूछे पश्चिम साइड</t>
+  </si>
+  <si>
+    <t>गोड़ वाला</t>
+  </si>
+  <si>
+    <t>पश्चिम सेमर</t>
+  </si>
+  <si>
+    <t>सुबाष नदी के किनारे</t>
+  </si>
+  <si>
+    <t>नदी के पार</t>
+  </si>
+  <si>
+    <t>नदी पानी में</t>
+  </si>
+  <si>
+    <t>पिज्जावा वाला</t>
+  </si>
+  <si>
+    <t>ज़ीनत दादी</t>
+  </si>
+  <si>
+    <t>रामा नदी के पार</t>
+  </si>
+  <si>
+    <t>घर</t>
+  </si>
+  <si>
+    <t>9817 ,9810 ,9811 , 9810</t>
   </si>
 </sst>
 </file>
@@ -1072,12 +1144,13 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.26953125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.1796875" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" style="3"/>
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="23.7265625" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1099,6 +1172,9 @@
       <c r="F1" s="4" t="s">
         <v>80</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
@@ -1117,7 +1193,9 @@
         <v>84</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1137,7 +1215,9 @@
         <v>84</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1159,6 +1239,9 @@
       <c r="F4" s="8" t="s">
         <v>87</v>
       </c>
+      <c r="G4" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1179,6 +1262,9 @@
       <c r="F5" s="8" t="s">
         <v>82</v>
       </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -1197,6 +1283,9 @@
         <v>84</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6" s="8" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1215,6 +1304,9 @@
         <v>84</v>
       </c>
       <c r="F7" s="1"/>
+      <c r="G7" s="8" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -1233,6 +1325,9 @@
         <v>84</v>
       </c>
       <c r="F8" s="1"/>
+      <c r="G8" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1253,6 +1348,9 @@
       <c r="F9" s="8" t="s">
         <v>88</v>
       </c>
+      <c r="G9" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -1271,6 +1369,9 @@
         <v>84</v>
       </c>
       <c r="F10" s="1"/>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1289,6 +1390,9 @@
         <v>84</v>
       </c>
       <c r="F11" s="1"/>
+      <c r="G11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -1307,6 +1411,9 @@
         <v>84</v>
       </c>
       <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1325,6 +1432,9 @@
         <v>84</v>
       </c>
       <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -1343,6 +1453,9 @@
         <v>84</v>
       </c>
       <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1361,6 +1474,9 @@
         <v>84</v>
       </c>
       <c r="F15" s="1"/>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -1379,8 +1495,11 @@
         <v>84</v>
       </c>
       <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1452</v>
       </c>
@@ -1397,8 +1516,11 @@
         <v>84</v>
       </c>
       <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1452</v>
       </c>
@@ -1417,8 +1539,11 @@
       <c r="F18" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1452</v>
       </c>
@@ -1435,13 +1560,16 @@
         <v>84</v>
       </c>
       <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1450</v>
       </c>
-      <c r="B20" s="6">
-        <v>9568</v>
+      <c r="B20" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1453,8 +1581,11 @@
         <v>84</v>
       </c>
       <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>2007</v>
       </c>
@@ -1471,8 +1602,11 @@
         <v>84</v>
       </c>
       <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1173</v>
       </c>
@@ -1488,25 +1622,30 @@
       <c r="E22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>9817981098119810</v>
-      </c>
-      <c r="B23" s="6">
         <v>0</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>46</v>
+      <c r="D23" s="7">
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/public/jamin_record.xlsx
+++ b/public/jamin_record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Desktop\jamin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Desktop\jamin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB381DE-5E4C-489B-9528-6984B0778664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045C5C0D-9EDA-4735-B41E-CB23B1B03EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="116">
   <si>
     <t>0.3.7</t>
   </si>
@@ -101,9 +101,6 @@
     <t>0.8.6</t>
   </si>
   <si>
-    <t>0.11.13</t>
-  </si>
-  <si>
     <t>0.1.2</t>
   </si>
   <si>
@@ -287,33 +284,15 @@
     <t>9597/12405</t>
   </si>
   <si>
-    <t>wrong correct rakba is 0.5.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">correct will be 0.1.0 </t>
-  </si>
-  <si>
     <t>Correct</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Dispute</t>
-  </si>
-  <si>
-    <t>Need correct divide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove from list not </t>
-  </si>
-  <si>
     <t>localName</t>
   </si>
   <si>
-    <t>धोबी वाला</t>
-  </si>
-  <si>
     <t>सेमर वाला उत्तर</t>
   </si>
   <si>
@@ -332,9 +311,6 @@
     <t>नगेशेर वाला</t>
   </si>
   <si>
-    <t>चाभ बस</t>
-  </si>
-  <si>
     <t>घर बगीचा</t>
   </si>
   <si>
@@ -378,6 +354,39 @@
   </si>
   <si>
     <t>9817 ,9810 ,9811 , 9810</t>
+  </si>
+  <si>
+    <t>धोबी वाला के बगल में</t>
+  </si>
+  <si>
+    <t>चाभ बास</t>
+  </si>
+  <si>
+    <t>0.5.5</t>
+  </si>
+  <si>
+    <t>Wrong in the list that is 0.11.13</t>
+  </si>
+  <si>
+    <t>0.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove from list and Add in Md. Ali rakba 0.4.0 </t>
+  </si>
+  <si>
+    <t>0.1.0</t>
+  </si>
+  <si>
+    <t>Need to divide correctly</t>
+  </si>
+  <si>
+    <t>Added in list and removed from Md.Ali</t>
+  </si>
+  <si>
+    <t>बद्री वाला</t>
+  </si>
+  <si>
+    <t>Wrong in the list that is  0.3.9 rest addin md. Ali</t>
   </si>
 </sst>
 </file>
@@ -755,7 +764,7 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
@@ -764,7 +773,7 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
@@ -773,7 +782,7 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -782,7 +791,7 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
@@ -791,7 +800,7 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
@@ -800,7 +809,7 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
@@ -809,7 +818,7 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
@@ -818,7 +827,7 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
@@ -827,7 +836,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
@@ -836,7 +845,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
@@ -845,7 +854,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
@@ -854,7 +863,7 @@
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
@@ -863,7 +872,7 @@
     </row>
     <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
@@ -872,7 +881,7 @@
     </row>
     <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
@@ -881,7 +890,7 @@
     </row>
     <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
@@ -890,7 +899,7 @@
     </row>
     <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
@@ -899,7 +908,7 @@
     </row>
     <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
@@ -908,7 +917,7 @@
     </row>
     <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
@@ -917,7 +926,7 @@
     </row>
     <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
@@ -998,7 +1007,7 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
@@ -1007,7 +1016,7 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
@@ -1016,7 +1025,7 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
@@ -1034,7 +1043,7 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -1043,7 +1052,7 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
@@ -1052,7 +1061,7 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
@@ -1061,7 +1070,7 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
@@ -1070,7 +1079,7 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
@@ -1079,7 +1088,7 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
@@ -1088,7 +1097,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
@@ -1097,7 +1106,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
@@ -1106,7 +1115,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
@@ -1115,7 +1124,7 @@
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
@@ -1124,7 +1133,7 @@
     </row>
     <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
@@ -1141,7 +1150,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.26953125" style="3" customWidth="1"/>
@@ -1149,31 +1158,31 @@
     <col min="3" max="3" width="12.1796875" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" style="3"/>
     <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="6" width="23.7265625" customWidth="1"/>
+    <col min="6" max="6" width="37.26953125" customWidth="1"/>
     <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1190,11 +1199,11 @@
         <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -1212,11 +1221,11 @@
         <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H3" s="1"/>
     </row>
@@ -1234,13 +1243,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1251,19 +1260,19 @@
         <v>9628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="D5" s="6">
-        <v>87</v>
+        <v>39.375</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1274,17 +1283,17 @@
         <v>9615</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6">
         <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1295,17 +1304,17 @@
         <v>9823</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6">
         <v>46.2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1316,17 +1325,17 @@
         <v>9830</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6">
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1337,19 +1346,19 @@
         <v>9834</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="D9" s="6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1360,17 +1369,17 @@
         <v>9835</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6">
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1381,17 +1390,17 @@
         <v>9825</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="6">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1402,17 +1411,17 @@
         <v>9826</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="6">
         <v>29.25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1420,7 +1429,7 @@
         <v>1452</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -1429,11 +1438,11 @@
         <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1444,17 +1453,17 @@
         <v>9759</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="6">
         <v>23.5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1465,17 +1474,17 @@
         <v>9772</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="6">
         <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1486,17 +1495,17 @@
         <v>9781</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="6">
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1507,17 +1516,17 @@
         <v>9780</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="6">
         <v>20.100000000000001</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1528,19 +1537,19 @@
         <v>9766</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="D18" s="6">
-        <v>26</v>
+        <v>7.5</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1551,17 +1560,17 @@
         <v>9614</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="6">
         <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1569,7 +1578,7 @@
         <v>1450</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1578,11 +1587,11 @@
         <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1593,17 +1602,17 @@
         <v>9746</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="6">
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1614,16 +1623,16 @@
         <v>9578</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="6">
         <v>34.75</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1631,20 +1640,66 @@
         <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B24" s="3">
+        <v>9467</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B25" s="3">
+        <v>9466</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>25.5</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1799,7 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
@@ -1762,7 +1817,7 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -1771,7 +1826,7 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
@@ -1780,7 +1835,7 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
@@ -1789,7 +1844,7 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
@@ -1798,7 +1853,7 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
@@ -1807,7 +1862,7 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
@@ -1816,7 +1871,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
@@ -1825,7 +1880,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
@@ -1834,7 +1889,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
@@ -1843,7 +1898,7 @@
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
@@ -1861,7 +1916,7 @@
     </row>
     <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
@@ -1870,7 +1925,7 @@
     </row>
     <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
@@ -1879,7 +1934,7 @@
     </row>
     <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
@@ -1888,7 +1943,7 @@
     </row>
     <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
@@ -1910,7 +1965,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1">
         <f t="shared" ref="B1:B20" si="0">LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
@@ -1927,7 +1982,7 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1">
         <f t="shared" si="0"/>
@@ -1942,7 +1997,7 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
@@ -1951,7 +2006,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
@@ -1969,7 +2024,7 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
@@ -1987,7 +2042,7 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
@@ -1996,7 +2051,7 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
@@ -2005,7 +2060,7 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -2014,7 +2069,7 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
@@ -2023,7 +2078,7 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
@@ -2032,7 +2087,7 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
@@ -2041,7 +2096,7 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
@@ -2050,7 +2105,7 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
@@ -2059,7 +2114,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
@@ -2068,7 +2123,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
@@ -2077,7 +2132,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
@@ -2086,7 +2141,7 @@
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
@@ -2117,7 +2172,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1">
         <f>LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>

--- a/public/jamin_record.xlsx
+++ b/public/jamin_record.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Desktop\jamin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045C5C0D-9EDA-4735-B41E-CB23B1B03EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5945CA91-8F81-49A8-A0F2-986A998FB976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="engineer Dada details" sheetId="1" r:id="rId1"/>
-    <sheet name="Md. Dada details" sheetId="2" r:id="rId2"/>
+    <sheet name="Md_Ali_details" sheetId="2" r:id="rId2"/>
     <sheet name="M.k.khan Details" sheetId="3" r:id="rId3"/>
     <sheet name="bade dada details" sheetId="4" r:id="rId4"/>
     <sheet name="master dada details" sheetId="5" r:id="rId5"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="119">
   <si>
     <t>0.3.7</t>
   </si>
@@ -387,6 +387,15 @@
   </si>
   <si>
     <t>Wrong in the list that is  0.3.9 rest addin md. Ali</t>
+  </si>
+  <si>
+    <t>Removed and Added in M.k.khan</t>
+  </si>
+  <si>
+    <t>0.2.9</t>
+  </si>
+  <si>
+    <t>Added in Md Ali 0.2.9</t>
   </si>
 </sst>
 </file>
@@ -943,204 +952,431 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="12.6328125" style="3"/>
+    <col min="6" max="6" width="29.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B2" s="3">
+        <v>9879</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <f t="shared" ref="B1:B20" si="0">LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
-        <v>67</v>
-      </c>
-      <c r="C1" s="1">
-        <f>SUM(B:B)</f>
-        <v>2096</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <f>INT(C1/400) &amp; "." &amp; INT(MOD(C1,400)/20) &amp; "." &amp; MOD(MOD(C1,400),20)</f>
-        <v>5.4.16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="1">
+        <f>IF(C2="","",VALUE(_xlfn.TEXTBEFORE(C2,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C2,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C2,".",2))*0.375)</f>
+        <v>25.125</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B3" s="3">
+        <v>9855</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1">
-        <f t="shared" si="0"/>
-        <v>447</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D22" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <v>77.625</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9839</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1">
-        <f t="shared" si="0"/>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>44.625</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B5" s="3">
+        <v>7027</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>26.25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9760</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>25.125</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B7" s="3">
+        <v>9629</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>7.125</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9486</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9467</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B10" s="3">
+        <v>9466</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9835</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9805</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>10.125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9807</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>17.625</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9599</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9600</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>10.875</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9596</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>76.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9781</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>17.625</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9782</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>29.625</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9614</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>82.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>2007</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9746</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>82.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>1173</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9875</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>116</v>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>43.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9766</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>18.375</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{0A2671B1-1588-4FF0-9B05-702F684C477A}">
+      <formula1>"Correct,Disputed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/public/jamin_record.xlsx
+++ b/public/jamin_record.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Appinventiv\Desktop\jamin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5945CA91-8F81-49A8-A0F2-986A998FB976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2711E7-68F9-4B82-83DF-13C1D0A10005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="engineer Dada details" sheetId="1" r:id="rId1"/>
+    <sheet name="md_Aslam_Khan" sheetId="1" r:id="rId1"/>
     <sheet name="Md_Ali_details" sheetId="2" r:id="rId2"/>
     <sheet name="M.k.khan Details" sheetId="3" r:id="rId3"/>
-    <sheet name="bade dada details" sheetId="4" r:id="rId4"/>
-    <sheet name="master dada details" sheetId="5" r:id="rId5"/>
-    <sheet name="Copy of master dada details 1" sheetId="6" r:id="rId6"/>
-    <sheet name="Copy of master dada details" sheetId="7" r:id="rId7"/>
+    <sheet name="Md._Islam_Khan" sheetId="4" r:id="rId4"/>
+    <sheet name="Junaid_Khan" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="117">
   <si>
     <t>0.3.7</t>
   </si>
@@ -59,18 +57,6 @@
     <t>0.3.10</t>
   </si>
   <si>
-    <t>Total Dhur</t>
-  </si>
-  <si>
-    <t>total dhur</t>
-  </si>
-  <si>
-    <t>Total Jamin</t>
-  </si>
-  <si>
-    <t>total jamin</t>
-  </si>
-  <si>
     <t>1.2.7</t>
   </si>
   <si>
@@ -230,9 +216,6 @@
     <t>0.5.17</t>
   </si>
   <si>
-    <t>0.0.16</t>
-  </si>
-  <si>
     <t>0.4.13</t>
   </si>
   <si>
@@ -374,9 +357,6 @@
     <t xml:space="preserve">Remove from list and Add in Md. Ali rakba 0.4.0 </t>
   </si>
   <si>
-    <t>0.1.0</t>
-  </si>
-  <si>
     <t>Need to divide correctly</t>
   </si>
   <si>
@@ -386,16 +366,28 @@
     <t>बद्री वाला</t>
   </si>
   <si>
-    <t>Wrong in the list that is  0.3.9 rest addin md. Ali</t>
-  </si>
-  <si>
     <t>Removed and Added in M.k.khan</t>
   </si>
   <si>
-    <t>0.2.9</t>
-  </si>
-  <si>
-    <t>Added in Md Ali 0.2.9</t>
+    <t>9617/12407</t>
+  </si>
+  <si>
+    <t>9794 , 9769 , 9797, 9793</t>
+  </si>
+  <si>
+    <t>0.1.14</t>
+  </si>
+  <si>
+    <t>0.1.15</t>
+  </si>
+  <si>
+    <t>Added in Md Ali 0.1.15</t>
+  </si>
+  <si>
+    <t>Added in Md Ali 0.4.0</t>
+  </si>
+  <si>
+    <t>Wrong in the list that is  0.3.9  rest 0.1.15 add in Md. Ali</t>
   </si>
 </sst>
 </file>
@@ -688,261 +680,513 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="3"/>
+    <col min="4" max="4" width="12.6328125" style="3"/>
+    <col min="5" max="5" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1046</v>
+      </c>
+      <c r="B2" s="3">
+        <v>9844</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1">
-        <f t="shared" ref="B1:B26" si="0">LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
-        <v>62</v>
-      </c>
-      <c r="C1" s="1">
-        <f>SUM(B:B)</f>
-        <v>2134</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <f>INT(C1/400) &amp; "." &amp; INT(MOD(C1,400)/20) &amp; "." &amp; MOD(MOD(C1,400),20)</f>
-        <v>5.6.14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="6">
+        <f>IF(C2="","",VALUE(_xlfn.TEXTBEFORE(C2,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C2,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C2,".",2))*0.375)</f>
+        <v>23.25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1046</v>
+      </c>
+      <c r="B3" s="3">
+        <v>9842</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1">
-        <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D27" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <v>25.5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1046</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9741</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="0"/>
+        <v>32.25</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1047</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9882</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>37.125</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1047</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9847</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1047</v>
+      </c>
+      <c r="B7" s="3">
+        <v>9559</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>37.125</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1047</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9572</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>62.25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1450</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7027</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>8.25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1451</v>
+      </c>
+      <c r="B10" s="3">
+        <v>9629</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>7.875</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1451</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9467</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1">
+      <c r="D11" s="6">
+        <f t="shared" si="0"/>
+        <v>24.375</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1451</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9466</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6">
+        <f t="shared" si="0"/>
+        <v>25.875</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1452</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9834</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1452</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9835</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1452</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9759</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6">
+        <f t="shared" si="0"/>
+        <v>23.625</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1452</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9781</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" si="0"/>
+        <v>15.375</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1452</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9782</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="6">
+        <f t="shared" si="0"/>
+        <v>29.625</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1452</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9766</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6">
+        <f t="shared" si="0"/>
+        <v>16.875</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1452</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9618</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="6">
+        <f t="shared" si="0"/>
+        <v>71.625</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1452</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9607</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="6">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1452</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9609</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="6">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1452</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9610</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="D22" s="6">
+        <f t="shared" si="0"/>
+        <v>79.5</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1452</v>
+      </c>
+      <c r="B23" s="3">
+        <v>9799</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="0"/>
+        <v>5.625</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1450</v>
+      </c>
+      <c r="B24" s="3">
+        <v>9568</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2007</v>
+      </c>
+      <c r="B25" s="3">
+        <v>9746</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
+      <c r="D25" s="6">
+        <f t="shared" si="0"/>
+        <v>48.75</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1173</v>
+      </c>
+      <c r="B26" s="3">
+        <v>9875</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="6">
+        <f t="shared" si="0"/>
+        <v>43.875</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1452</v>
+      </c>
+      <c r="B27" s="3">
+        <v>9788</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="6">
+        <f t="shared" si="0"/>
+        <v>5.625</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E27" xr:uid="{9155D37E-0268-4C14-B44B-BF03E755BB37}">
+      <formula1>"Correct,Disputed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -952,7 +1196,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.6328125" style="3"/>
@@ -961,25 +1205,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -997,7 +1241,7 @@
         <v>25.125</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -1009,14 +1253,14 @@
         <v>9855</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D22" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <f t="shared" ref="D3:D23" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
         <v>77.625</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1"/>
     </row>
@@ -1028,14 +1272,14 @@
         <v>9839</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
         <v>44.625</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1053,7 +1297,7 @@
         <v>26.25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1071,7 +1315,7 @@
         <v>25.125</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1082,14 +1326,14 @@
         <v>9629</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>7.125</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1100,14 +1344,14 @@
         <v>9486</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1118,17 +1362,17 @@
         <v>9467</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
         <v>109</v>
-      </c>
-      <c r="D9" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1139,17 +1383,17 @@
         <v>9466</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
         <v>109</v>
-      </c>
-      <c r="D10" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1160,14 +1404,14 @@
         <v>9835</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>19.5</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1178,14 +1422,14 @@
         <v>9805</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
         <v>10.125</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1196,14 +1440,14 @@
         <v>9807</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
         <v>17.625</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1214,14 +1458,14 @@
         <v>9599</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1232,14 +1476,14 @@
         <v>9600</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
         <v>10.875</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1250,14 +1494,14 @@
         <v>9596</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
         <v>76.5</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1268,14 +1512,14 @@
         <v>9781</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
         <v>17.625</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1286,14 +1530,14 @@
         <v>9782</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="0"/>
         <v>29.625</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1304,14 +1548,14 @@
         <v>9614</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="0"/>
         <v>82.5</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1322,14 +1566,14 @@
         <v>9746</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
         <v>82.5</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
@@ -1340,14 +1584,14 @@
         <v>9875</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="0"/>
         <v>43.5</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1358,17 +1602,38 @@
         <v>9766</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="0"/>
-        <v>18.375</v>
+        <v>13.125</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B23" s="3">
+        <v>9834</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1394,31 +1659,31 @@
     <col min="3" max="3" width="12.1796875" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" style="3"/>
     <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="6" width="37.26953125" customWidth="1"/>
+    <col min="6" max="6" width="47.36328125" customWidth="1"/>
     <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1435,11 +1700,11 @@
         <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -1451,17 +1716,17 @@
         <v>9577</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H3" s="1"/>
     </row>
@@ -1479,13 +1744,13 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1496,19 +1761,19 @@
         <v>9628</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D5" s="6">
         <v>39.375</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1519,17 +1784,17 @@
         <v>9615</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6">
         <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1540,17 +1805,17 @@
         <v>9823</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6">
         <v>46.2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1561,17 +1826,17 @@
         <v>9830</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6">
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1582,19 +1847,19 @@
         <v>9834</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1605,17 +1870,17 @@
         <v>9835</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6">
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1626,17 +1891,17 @@
         <v>9825</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1647,17 +1912,17 @@
         <v>9826</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="6">
         <v>29.25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,20 +1930,20 @@
         <v>1452</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6">
         <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1689,17 +1954,17 @@
         <v>9759</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D14" s="6">
         <v>23.5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1710,17 +1975,17 @@
         <v>9772</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D15" s="6">
         <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1731,17 +1996,17 @@
         <v>9781</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D16" s="6">
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1752,17 +2017,17 @@
         <v>9780</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D17" s="6">
         <v>20.100000000000001</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1773,19 +2038,19 @@
         <v>9766</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6">
         <v>7.5</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1796,17 +2061,17 @@
         <v>9614</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D19" s="6">
         <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1814,7 +2079,7 @@
         <v>1450</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1823,11 +2088,11 @@
         <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1838,17 +2103,17 @@
         <v>9746</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1859,16 +2124,16 @@
         <v>9578</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D22" s="6">
         <v>34.75</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
@@ -1876,20 +2141,20 @@
         <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1900,19 +2165,19 @@
         <v>9467</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D24" s="3">
         <v>24.5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1929,13 +2194,13 @@
         <v>25.5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1953,240 +2218,477 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.6328125" style="3"/>
+    <col min="2" max="2" width="21.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1046</v>
+      </c>
+      <c r="B2" s="3">
+        <v>9880</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1">
-        <f t="shared" ref="B1:B24" si="0">LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
-        <v>255</v>
-      </c>
-      <c r="C1" s="1">
-        <f>SUM(B:B)</f>
-        <v>2102</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <f>INT(C1/400) &amp; "." &amp; INT(MOD(C1,400)/20) &amp; "." &amp; MOD(MOD(C1,400),20)</f>
-        <v>5.5.2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="6">
+        <f>IF(C2="","",VALUE(_xlfn.TEXTBEFORE(C2,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C2,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C2,".",2))*0.375)</f>
+        <v>95.625</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B3" s="3">
+        <v>7027</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D25" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <v>26.25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9760</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="0"/>
+        <v>13.875</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9758</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>4.125</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9616</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>84.375</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B7" s="3">
+        <v>9757</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>4.875</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9724</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9629</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>7.875</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B10" s="3">
+        <v>9486</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>26.25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9487</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9827</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="6">
+        <f t="shared" si="0"/>
+        <v>43.5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9835</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="D13" s="6">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9597</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" si="0"/>
+        <v>44.25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9598</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="6">
+        <f t="shared" si="0"/>
+        <v>76.5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9759</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" si="0"/>
+        <v>10.875</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9782</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6">
+        <f t="shared" si="0"/>
+        <v>46.875</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9784</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
+      <c r="D18" s="6">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9785</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="D19" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9766</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="6">
+        <f t="shared" si="0"/>
+        <v>16.875</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="6">
+        <f t="shared" si="0"/>
+        <v>4.125</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9795</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>2007</v>
+      </c>
+      <c r="B23" s="3">
+        <v>9746</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="0"/>
+        <v>41.25</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>1173</v>
+      </c>
+      <c r="B24" s="3">
+        <v>9578</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="0"/>
+        <v>48.375</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>111</v>
+      <c r="D25" s="6">
+        <f t="shared" si="0"/>
+        <v>41.625</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E25" xr:uid="{EA7FC2C2-4D01-4050-9248-B89F1D6624BD}">
+      <formula1>"Dispute,Correct"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2196,254 +2698,407 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="12.6328125" style="3"/>
+    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1046</v>
+      </c>
+      <c r="B2" s="3">
+        <v>9861</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="1">
+        <f>IF(C2="","",VALUE(_xlfn.TEXTBEFORE(C2,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C2,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C2,".",2))*0.375)</f>
+        <v>88.5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B3" s="3">
+        <v>9853</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D21" si="0">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <v>16.5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9840</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>22.875</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1047</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9855</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="1">
+        <f>IF(C2="","",VALUE(_xlfn.TEXTBEFORE(C2,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C2,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C2,".",2))*0.375)</f>
+        <v>88.5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9838</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" ref="D6:D21" si="1">IF(C3="","",VALUE(_xlfn.TEXTBEFORE(C3,"."))*60+VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(C3,"."),"."))*7.5+VALUE(_xlfn.TEXTAFTER(C3,".",2))*0.375)</f>
+        <v>16.5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7027</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="1"/>
+        <v>22.875</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1450</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9760</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="1"/>
+        <v>55.5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9629</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="1"/>
+        <v>25.125</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1451</v>
+      </c>
+      <c r="B10" s="3">
+        <v>9486</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="1"/>
+        <v>26.625</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9837</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1">
-        <f t="shared" ref="B1:B20" si="0">LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
-        <v>236</v>
-      </c>
-      <c r="C1" s="1">
-        <f>SUM(B:B)</f>
-        <v>2090</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <f>INT(C1/400) &amp; "." &amp; INT(MOD(C1,400)/20) &amp; "." &amp; MOD(MOD(C1,400),20)</f>
-        <v>5.4.10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="D11" s="1">
+        <f t="shared" si="1"/>
+        <v>25.125</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9835</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="1"/>
+        <v>7.125</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9807</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="1">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D13" s="1">
+        <f t="shared" si="1"/>
+        <v>37.875</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9593</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D14" s="1">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9592</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9782</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="1"/>
+        <v>15.75</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9766</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="1"/>
+        <v>92.25</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9618</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D18" s="1">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>1452</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9828</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="1"/>
+        <v>46.5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>1173</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9856</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+      <c r="D20" s="1">
+        <f t="shared" si="1"/>
+        <v>16.875</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>2007</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9746</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="1"/>
+        <v>71.25</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1">
-        <f>LEFT(A1,FIND(".",A1)-1)*400 + MID(A1,FIND(".",A1)+1,FIND(".",A1,FIND(".",A1)+1)-FIND(".",A1)-1)*20 + RIGHT(A1,LEN(A1)-FIND(".",A1,FIND(".",A1)+1))</f>
-        <v>236</v>
-      </c>
-      <c r="C1" s="1">
-        <f>SUM(B:B)</f>
-        <v>236</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <f>INT(C1/400) &amp; "." &amp; INT(MOD(C1,400)/20) &amp; "." &amp; MOD(MOD(C1,400),20)</f>
-        <v>0.11.16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E21" xr:uid="{C2CD90A7-588F-48D9-A4F4-B79DDB6DC97F}">
+      <formula1>"Dispute,Correct"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>